--- a/docs/AI智能体与合同智能化功能对比表.xlsx
+++ b/docs/AI智能体与合同智能化功能对比表.xlsx
@@ -12,6 +12,7 @@
     <sheet name="智能体功能明细" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="与原合同关系" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="投资与工作量" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="模型依赖度分析" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">与原合同关系!$4:$4</definedName>
@@ -20,6 +21,8 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">投资与工作量!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">智能体功能明细!$4:$4</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">智能体功能明细!$A$3:$E$39</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">模型依赖度分析!$3:$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">模型依赖度分析!$A$3:$F$39</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="353">
   <si>
     <t xml:space="preserve">合同约定智能化功能 与 新增AI智能体功能 对比表</t>
   </si>
@@ -1430,6 +1433,810 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">中台算法仓库、算力调度、事件中心、全文检索、移动端等能力直接复用，本次不投入工作量。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本次建设内容的「模型依赖度」分析——回答“模型都一样，区别在哪”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结论：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">36 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个三级功能项中，仅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">项（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的输出结果会随底层大模型更换而变化；其余 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">项（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">86.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）无论选用哪家模型都必须自行建设。本项目不采购大模型，模型与算力由省政务云统一提供，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">元列支。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">与大模型的关系</t>
+  </si>
+  <si>
+    <t xml:space="preserve">换个模型会不会不一样</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多模态涉渔违法行为推理模型与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Prompt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工程构建</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直接依赖大模型</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">会 —— 换模型需重新调优与验证</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法条真实性硬约束校验与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条文一致性过滤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">约束</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校验模型（因模型不可信才建）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不会 —— 正因模型不可靠才必须建</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人机协同确认工作流与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">能力一键无缝接管降级开关</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本地领域数据资产（模型里没有）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不会 —— 本地数据资产，任何模型都没有</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">统一知识库与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检索中枢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">视频</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">雷达</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/AIS/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">电子围栏事件实时接入与协议标准化</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工程与系统集成（与模型无关）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不会 —— 工程能力，与模型无关</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">密集向量与倒排索引双路混合检索（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hybrid RAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法规语义重排序（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rerank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）与上下文窗口动态装配</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">执法人员</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">执法船艇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无人机就绪状态与实时定位感知</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">移动端（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">APP/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短信）一键派发与协同通知</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多智能体协作工作流编排（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ReAct/DAG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">编排引擎）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">统一工具注册中心与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAPI/Function Calling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">适配</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">业务规则与流程（与模型无关）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不会 —— 业务规则，与模型无关</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">研判交互工作台（人工审核、修正、确认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">驳回界面）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">分类统计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">答辩口径：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本项目不采购大模型。模型与算力由省政务云统一提供，本项目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">67 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万元中 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">元用于购买模型，买的是让模型在渔政执法场景可用、可信、可审计的那部分工程。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型是通用底座，不含江苏省渔政裁量基准、不知道苏渔政</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的航速与抗风浪等级、不知道本平台有哪些业务接口——这些只能自建。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直接问大模型“这条船违法吗、该罚多少”，它会编造法条。本次第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">类 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">项（法条硬校验、入参沙箱、状态机自愈、一键降级）正是为约束模型而建。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同一款发动机可以装在不同的车上。模型相同不代表系统相同，差异在数据、工程、业务规则与合规管控。</t>
     </r>
   </si>
 </sst>
@@ -1442,7 +2249,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1586,8 +2393,74 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F4E79"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFC00000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFC00000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFC00000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF404040"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF404040"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1636,6 +2509,36 @@
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -1686,7 +2589,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1840,6 +2743,130 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1852,7 +2879,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1916,6 +2943,46 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1933,7 +3000,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1942,7 +3009,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFBDD7EE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1954,11 +3021,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFDCE6F1"/>
       <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFFFE699"/>
+      <rgbColor rgb="FFC6E0B4"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1974,7 +3041,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E79"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1985,6 +3052,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -4157,4 +5228,904 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F15" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="48" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>240</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="F21" s="49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="51" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="51" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F24" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="51" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>339</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F25" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="51" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F26" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="51" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>341</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="51" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="51" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="51" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="51" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F32" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="51" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="F33" s="52" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="54" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>346</v>
+      </c>
+      <c r="E35" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="54" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="D36" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="54" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F37" s="55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F38" s="55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="54" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="D39" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F39" s="55" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="57" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="58" t="s">
+        <v>326</v>
+      </c>
+      <c r="C42" s="59" t="n">
+        <f aca="false">COUNTIF($E$4:$E$39,B42&amp;"*")</f>
+        <v>5</v>
+      </c>
+      <c r="D42" s="60" t="n">
+        <f aca="false">C42/$C$47</f>
+        <v>0.138888888888889</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="C43" s="59" t="n">
+        <f aca="false">COUNTIF($E$4:$E$39,B43&amp;"*")</f>
+        <v>4</v>
+      </c>
+      <c r="D43" s="60" t="n">
+        <f aca="false">C43/$C$47</f>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="62" t="s">
+        <v>332</v>
+      </c>
+      <c r="C44" s="59" t="n">
+        <f aca="false">COUNTIF($E$4:$E$39,B44&amp;"*")</f>
+        <v>9</v>
+      </c>
+      <c r="D44" s="60" t="n">
+        <f aca="false">C44/$C$47</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="C45" s="59" t="n">
+        <f aca="false">COUNTIF($E$4:$E$39,B45&amp;"*")</f>
+        <v>12</v>
+      </c>
+      <c r="D45" s="60" t="n">
+        <f aca="false">C45/$C$47</f>
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="C46" s="59" t="n">
+        <f aca="false">COUNTIF($E$4:$E$39,B46&amp;"*")</f>
+        <v>6</v>
+      </c>
+      <c r="D46" s="60" t="n">
+        <f aca="false">C46/$C$47</f>
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="C47" s="66" t="n">
+        <f aca="false">SUM(C42:C46)</f>
+        <v>36</v>
+      </c>
+      <c r="D47" s="67" t="n">
+        <f aca="false">C47/$C$47</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="68" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="69" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="69" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="69" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="69" t="s">
+        <v>352</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F39"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="8" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>